--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LOGROBASKET LOGI7.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LOGROBASKET LOGI7.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>45.9832</v>
+        <v>39.5338</v>
       </c>
       <c r="E2" t="n">
-        <v>48.1163</v>
+        <v>40.8487</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1332</v>
+        <v>-1.315199999999999</v>
       </c>
       <c r="G2" t="n">
         <v>16.1693</v>
@@ -610,13 +610,13 @@
         <v>31.2178</v>
       </c>
       <c r="S2" t="n">
-        <v>12.217</v>
+        <v>5.7673</v>
       </c>
       <c r="T2" t="n">
-        <v>14.3784</v>
+        <v>7.1106</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.1613</v>
+        <v>-1.3432</v>
       </c>
       <c r="V2" t="n">
         <v>16.1403</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>11.0534</v>
+        <v>22.8584</v>
       </c>
       <c r="E3" t="n">
-        <v>13.5742</v>
+        <v>30.7293</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.521299999999999</v>
+        <v>-7.870399999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>10.9629</v>
+        <v>9.3719</v>
       </c>
       <c r="H3" t="n">
-        <v>17.8647</v>
+        <v>2.3083</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.9018</v>
+        <v>7.0637</v>
       </c>
       <c r="J3" t="n">
-        <v>27.8101</v>
+        <v>31.3797</v>
       </c>
       <c r="K3" t="n">
-        <v>17.2405</v>
+        <v>8.241300000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5697</v>
+        <v>23.1384</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.8466</v>
+        <v>-22.0078</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6241999999999996</v>
+        <v>-5.9329</v>
       </c>
       <c r="O3" t="n">
-        <v>-17.4712</v>
+        <v>-16.0749</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8731</v>
+        <v>5.411</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34.7559</v>
+        <v>-36.0046</v>
       </c>
       <c r="R3" t="n">
-        <v>32.8827</v>
+        <v>41.4155</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9704</v>
+        <v>-8.2273</v>
       </c>
       <c r="T3" t="n">
-        <v>5.395300000000001</v>
+        <v>-3.1392</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.4249</v>
+        <v>-5.087899999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.006800000000000139</v>
+        <v>16.303</v>
       </c>
       <c r="W3" t="n">
-        <v>15.1249</v>
+        <v>38.4931</v>
       </c>
       <c r="X3" t="n">
-        <v>-15.1319</v>
+        <v>-22.1901</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0131</v>
+        <v>9.9663</v>
       </c>
       <c r="E4" t="n">
-        <v>17.8744</v>
+        <v>10.0058</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.8614</v>
+        <v>-0.03930000000000033</v>
       </c>
       <c r="G4" t="n">
-        <v>9.3719</v>
+        <v>10.9629</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3083</v>
+        <v>17.8647</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0637</v>
+        <v>-6.9018</v>
       </c>
       <c r="J4" t="n">
-        <v>31.3797</v>
+        <v>27.8101</v>
       </c>
       <c r="K4" t="n">
-        <v>8.241300000000001</v>
+        <v>17.2405</v>
       </c>
       <c r="L4" t="n">
-        <v>23.1384</v>
+        <v>10.5697</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.0078</v>
+        <v>-16.8466</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.9329</v>
+        <v>0.6241999999999996</v>
       </c>
       <c r="O4" t="n">
-        <v>-16.0749</v>
+        <v>-17.4712</v>
       </c>
       <c r="P4" t="n">
-        <v>5.411</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.0046</v>
+        <v>-34.7559</v>
       </c>
       <c r="R4" t="n">
-        <v>41.4155</v>
+        <v>32.8827</v>
       </c>
       <c r="S4" t="n">
-        <v>-26.0729</v>
+        <v>0.8832999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-15.9936</v>
+        <v>1.8271</v>
       </c>
       <c r="U4" t="n">
-        <v>-10.0789</v>
+        <v>-0.9433000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>16.303</v>
+        <v>-0.006800000000000139</v>
       </c>
       <c r="W4" t="n">
-        <v>38.4931</v>
+        <v>15.1249</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.1901</v>
+        <v>-15.1319</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7902</v>
+        <v>2.1097</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1414</v>
+        <v>0.4032000000000006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6486999999999999</v>
+        <v>1.7059</v>
       </c>
       <c r="G5" t="n">
-        <v>0.227</v>
+        <v>5.526</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3838</v>
+        <v>8.924099999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6106</v>
+        <v>-3.398200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0392</v>
+        <v>25.2232</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.6034</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0392</v>
+        <v>11.6197</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1878</v>
+        <v>-19.6971</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3838</v>
+        <v>-4.6791</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5714</v>
+        <v>-15.0175</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-34.7559</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>38.5018</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3119</v>
+        <v>-7.5908</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-3.3671</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2466</v>
+        <v>-4.2238</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8751</v>
+        <v>0.4280999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>13.3027</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7076</v>
+        <v>-12.8747</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VÁZQUEZ GIL</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.748000000000001</v>
+        <v>1.9561</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7817</v>
+        <v>1.2486</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5297</v>
+        <v>0.7074999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2128</v>
+        <v>0.227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7654000000000001</v>
+        <v>-0.3838</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.9783</v>
+        <v>0.6106</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2939</v>
+        <v>0.0392</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4381999999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8556000000000001</v>
+        <v>0.0392</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9189999999999999</v>
+        <v>0.1878</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2038</v>
+        <v>-0.3838</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1227</v>
+        <v>0.5714</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.538</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.3705</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3324</v>
+        <v>-0.146</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0242</v>
+        <v>0.0419</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3082</v>
+        <v>-0.1879</v>
       </c>
       <c r="V6" t="n">
-        <v>0.796</v>
+        <v>1.8751</v>
       </c>
       <c r="W6" t="n">
-        <v>1.026</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARZON JIMENEZ</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8669</v>
+        <v>0.4277000000000006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6231</v>
+        <v>7.7419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2438</v>
+        <v>-7.3148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1779</v>
+        <v>-7.982500000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4328</v>
+        <v>-1.603699999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6107</v>
+        <v>-6.3789</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0392</v>
+        <v>9.7523</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.9212999999999998</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0392</v>
+        <v>8.831000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1387</v>
+        <v>-17.7348</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4328</v>
+        <v>-2.5253</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5715</v>
+        <v>-15.2099</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>10.8223</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-7.9085</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>18.7309</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6889</v>
+        <v>1.8191</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5839</v>
+        <v>1.8297</v>
       </c>
       <c r="U7" t="n">
-        <v>0.105</v>
+        <v>-0.01059999999999997</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-4.2315</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.0687</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-8.3002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>J. GARZON JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5493</v>
+        <v>0.3208</v>
       </c>
       <c r="E8" t="n">
-        <v>6.213900000000001</v>
+        <v>0.1945</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.7631</v>
+        <v>0.1263</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.982500000000002</v>
+        <v>0.1779</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.603699999999999</v>
+        <v>-0.4328</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.3789</v>
+        <v>0.6107</v>
       </c>
       <c r="J8" t="n">
-        <v>9.7523</v>
+        <v>0.0392</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9212999999999998</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8.831000000000001</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-17.7348</v>
+        <v>0.1387</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.5253</v>
+        <v>-0.4328</v>
       </c>
       <c r="O8" t="n">
-        <v>-15.2099</v>
+        <v>0.5715</v>
       </c>
       <c r="P8" t="n">
-        <v>10.8223</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.9085</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>18.7309</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1577</v>
+        <v>0.1429</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3015</v>
+        <v>0.1553</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4588</v>
+        <v>-0.0124</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.2315</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4.0687</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-8.3002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>M. VÁZQUEZ GIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2113</v>
+        <v>-0.08249999999999957</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5965</v>
+        <v>-3.1933</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3852</v>
+        <v>3.1109</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1982999999999999</v>
+        <v>-2.2128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9937</v>
+        <v>0.7654000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.192</v>
+        <v>-2.9783</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8433</v>
+        <v>-1.2939</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0185</v>
+        <v>-0.4381999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>2.8248</v>
+        <v>-0.8556000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.0416</v>
+        <v>-0.9189999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02489999999999998</v>
+        <v>1.2038</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.0168</v>
+        <v>-2.1227</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.411099999999999</v>
+        <v>-3.538</v>
       </c>
       <c r="R9" t="n">
-        <v>4.5786</v>
+        <v>4.3705</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.7642</v>
+        <v>0.5019000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2588</v>
+        <v>0.6126</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5055000000000001</v>
+        <v>-0.1107</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5838</v>
+        <v>0.796</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>1.026</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Í. IBAÑEZ SERRANO</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4143</v>
+        <v>-2.0414</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4353</v>
+        <v>-2.6322</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9789</v>
+        <v>0.5907</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6834</v>
+        <v>-0.1982999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1059</v>
+        <v>0.9937</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5774</v>
+        <v>-1.192</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2171</v>
+        <v>3.8433</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6909</v>
+        <v>1.0185</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.908</v>
+        <v>2.8248</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4662</v>
+        <v>-4.0416</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7967</v>
+        <v>-0.02489999999999998</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6694</v>
+        <v>-4.0168</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4567</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-5.411099999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4973</v>
+        <v>4.5786</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8527000000000001</v>
+        <v>-1.5944</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1775</v>
+        <v>-1.2944</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6753</v>
+        <v>-0.2999999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.335</v>
+        <v>0.5838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.335</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>Í. IBAÑEZ SERRANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.1021</v>
+        <v>-4.4941</v>
       </c>
       <c r="E11" t="n">
-        <v>-20.2885</v>
+        <v>-1.6619</v>
       </c>
       <c r="F11" t="n">
-        <v>9.186299999999999</v>
+        <v>-2.832</v>
       </c>
       <c r="G11" t="n">
-        <v>-21.295</v>
+        <v>-3.6834</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.828900000000001</v>
+        <v>-1.1059</v>
       </c>
       <c r="I11" t="n">
-        <v>-12.4659</v>
+        <v>-2.5774</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.5551</v>
+        <v>-1.2171</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.2737</v>
+        <v>0.6909</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.2817</v>
+        <v>-1.908</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.739699999999999</v>
+        <v>-2.4662</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5556</v>
+        <v>-1.7967</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.1845</v>
+        <v>-0.6694</v>
       </c>
       <c r="P11" t="n">
-        <v>6.2438</v>
+        <v>1.4567</v>
       </c>
       <c r="Q11" t="n">
-        <v>-22.4768</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>28.7203</v>
+        <v>2.4973</v>
       </c>
       <c r="S11" t="n">
-        <v>7.5542</v>
+        <v>0.0675</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1475</v>
+        <v>0.5958</v>
       </c>
       <c r="U11" t="n">
-        <v>4.407</v>
+        <v>-0.5282</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.605300000000001</v>
+        <v>-2.335</v>
       </c>
       <c r="W11" t="n">
-        <v>10.596</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.2014</v>
+        <v>-2.335</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.0309</v>
+        <v>-6.7653</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.4759</v>
+        <v>-16.637</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4447</v>
+        <v>9.872</v>
       </c>
       <c r="G12" t="n">
         <v>2.4676</v>
@@ -1390,13 +1390,13 @@
         <v>13.1115</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.991399999999999</v>
+        <v>-3.7256</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.4004</v>
+        <v>-2.5613</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.5909</v>
+        <v>-1.1642</v>
       </c>
       <c r="V12" t="n">
         <v>0.9445999999999998</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.5954</v>
+        <v>-11.716</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.0051</v>
+        <v>-10.6392</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5906</v>
+        <v>-1.0767</v>
       </c>
       <c r="G13" t="n">
-        <v>5.526</v>
+        <v>-4.6051</v>
       </c>
       <c r="H13" t="n">
-        <v>8.924099999999999</v>
+        <v>0.2929000000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.398200000000001</v>
+        <v>-4.8976</v>
       </c>
       <c r="J13" t="n">
-        <v>25.2232</v>
+        <v>4.6639</v>
       </c>
       <c r="K13" t="n">
-        <v>13.6034</v>
+        <v>1.165</v>
       </c>
       <c r="L13" t="n">
-        <v>11.6197</v>
+        <v>3.499</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.6971</v>
+        <v>-9.268800000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6791</v>
+        <v>-0.8718999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.0175</v>
+        <v>-8.396599999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7463</v>
+        <v>-1.6651</v>
       </c>
       <c r="Q13" t="n">
-        <v>-34.7559</v>
+        <v>-15.817</v>
       </c>
       <c r="R13" t="n">
-        <v>38.5018</v>
+        <v>14.152</v>
       </c>
       <c r="S13" t="n">
-        <v>-25.2961</v>
+        <v>-4.1723</v>
       </c>
       <c r="T13" t="n">
-        <v>-13.775</v>
+        <v>-0.8834000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-11.5205</v>
+        <v>-3.2889</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4280999999999999</v>
+        <v>-1.2737</v>
       </c>
       <c r="W13" t="n">
-        <v>13.3027</v>
+        <v>1.3975</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.8747</v>
+        <v>-2.6712</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.9962</v>
+        <v>-19.289</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.5361</v>
+        <v>-24.267</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.46</v>
+        <v>4.9782</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5199</v>
+        <v>-21.295</v>
       </c>
       <c r="H14" t="n">
-        <v>7.827900000000001</v>
+        <v>-8.828900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.348</v>
+        <v>-12.4659</v>
       </c>
       <c r="J14" t="n">
-        <v>13.1225</v>
+        <v>-11.5551</v>
       </c>
       <c r="K14" t="n">
-        <v>11.1346</v>
+        <v>-6.2737</v>
       </c>
       <c r="L14" t="n">
-        <v>1.988</v>
+        <v>-5.2817</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.6425</v>
+        <v>-9.739699999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.3064</v>
+        <v>-2.5556</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.3359</v>
+        <v>-7.1845</v>
       </c>
       <c r="P14" t="n">
-        <v>-27.4716</v>
+        <v>6.2438</v>
       </c>
       <c r="Q14" t="n">
-        <v>-56.6083</v>
+        <v>-22.4768</v>
       </c>
       <c r="R14" t="n">
-        <v>29.1366</v>
+        <v>28.7203</v>
       </c>
       <c r="S14" t="n">
-        <v>15.8046</v>
+        <v>-0.6324000000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>13.2767</v>
+        <v>-0.831</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5281</v>
+        <v>0.1989000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.809199999999999</v>
+        <v>-3.605300000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>15.6731</v>
+        <v>10.596</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.4823</v>
+        <v>-14.2014</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-18.5165</v>
+        <v>-25.8949</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.3648</v>
+        <v>-21.0062</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.1517</v>
+        <v>-4.888699999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.6051</v>
+        <v>-28.6142</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2929000000000002</v>
+        <v>-4.6241</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.8976</v>
+        <v>-23.9899</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6639</v>
+        <v>-3.062400000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.165</v>
+        <v>1.1907</v>
       </c>
       <c r="L15" t="n">
-        <v>3.499</v>
+        <v>-4.253300000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.268800000000001</v>
+        <v>-25.5516</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8718999999999999</v>
+        <v>-5.8148</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.396599999999999</v>
+        <v>-19.7369</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6651</v>
+        <v>-6.659599999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.817</v>
+        <v>-47.4512</v>
       </c>
       <c r="R15" t="n">
-        <v>14.152</v>
+        <v>40.7914</v>
       </c>
       <c r="S15" t="n">
-        <v>-10.9729</v>
+        <v>-3.7854</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.609</v>
+        <v>-1.3615</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.3637</v>
+        <v>-2.4243</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2737</v>
+        <v>13.1649</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>30.8688</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.6712</v>
+        <v>-17.7042</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.0102</v>
+        <v>-26.6617</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.7305</v>
+        <v>-22.6239</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.2793</v>
+        <v>-4.038</v>
       </c>
       <c r="G16" t="n">
-        <v>-32.4334</v>
+        <v>-2.5199</v>
       </c>
       <c r="H16" t="n">
-        <v>-15.7884</v>
+        <v>7.827900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-16.6449</v>
+        <v>-10.348</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2526</v>
+        <v>13.1225</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.7445</v>
+        <v>11.1346</v>
       </c>
       <c r="L16" t="n">
-        <v>4.492</v>
+        <v>1.988</v>
       </c>
       <c r="M16" t="n">
-        <v>-30.1805</v>
+        <v>-15.6425</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.0436</v>
+        <v>-3.3064</v>
       </c>
       <c r="O16" t="n">
-        <v>-21.1367</v>
+        <v>-12.3359</v>
       </c>
       <c r="P16" t="n">
-        <v>-24.5582</v>
+        <v>-27.4716</v>
       </c>
       <c r="Q16" t="n">
-        <v>-62.6439</v>
+        <v>-56.6083</v>
       </c>
       <c r="R16" t="n">
-        <v>38.0857</v>
+        <v>29.1366</v>
       </c>
       <c r="S16" t="n">
-        <v>24.3655</v>
+        <v>6.1393</v>
       </c>
       <c r="T16" t="n">
-        <v>18.4456</v>
+        <v>5.188800000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>5.919700000000001</v>
+        <v>0.9505</v>
       </c>
       <c r="V16" t="n">
-        <v>3.615699999999999</v>
+        <v>-2.809199999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>27.7198</v>
+        <v>15.6731</v>
       </c>
       <c r="X16" t="n">
-        <v>-24.1041</v>
+        <v>-18.4823</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-41.7375</v>
+        <v>-42.5149</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.8248</v>
+        <v>-28.873</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.9131</v>
+        <v>-13.6422</v>
       </c>
       <c r="G17" t="n">
-        <v>-28.6142</v>
+        <v>-32.4334</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.6241</v>
+        <v>-15.7884</v>
       </c>
       <c r="I17" t="n">
-        <v>-23.9899</v>
+        <v>-16.6449</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.062400000000001</v>
+        <v>-2.2526</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1907</v>
+        <v>-6.7445</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.253300000000001</v>
+        <v>4.492</v>
       </c>
       <c r="M17" t="n">
-        <v>-25.5516</v>
+        <v>-30.1805</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.8148</v>
+        <v>-9.0436</v>
       </c>
       <c r="O17" t="n">
-        <v>-19.7369</v>
+        <v>-21.1367</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.659599999999999</v>
+        <v>-24.5582</v>
       </c>
       <c r="Q17" t="n">
-        <v>-47.4512</v>
+        <v>-62.6439</v>
       </c>
       <c r="R17" t="n">
-        <v>40.7914</v>
+        <v>38.0857</v>
       </c>
       <c r="S17" t="n">
-        <v>-19.6284</v>
+        <v>10.8606</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.1799</v>
+        <v>8.3034</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.4485</v>
+        <v>2.5568</v>
       </c>
       <c r="V17" t="n">
-        <v>13.1649</v>
+        <v>3.615699999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>30.8688</v>
+        <v>27.7198</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.7042</v>
+        <v>-24.1041</v>
       </c>
     </row>
     <row r="18">
@@ -1813,22 +1813,22 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-90.7089</v>
+        <v>-62.287</v>
       </c>
       <c r="E18" t="n">
-        <v>-49.49589999999999</v>
+        <v>-40.3617</v>
       </c>
       <c r="F18" t="n">
-        <v>-41.21420000000001</v>
+        <v>-21.9258</v>
       </c>
       <c r="G18" t="n">
-        <v>-58.64199999999998</v>
+        <v>-58.64199999999999</v>
       </c>
       <c r="H18" t="n">
         <v>19.5708</v>
       </c>
       <c r="I18" t="n">
-        <v>-78.2128</v>
+        <v>-78.21279999999999</v>
       </c>
       <c r="J18" t="n">
         <v>139.2445</v>
@@ -1837,7 +1837,7 @@
         <v>63.1765</v>
       </c>
       <c r="L18" t="n">
-        <v>76.06819999999999</v>
+        <v>76.0682</v>
       </c>
       <c r="M18" t="n">
         <v>-197.8855</v>
@@ -1849,7 +1849,7 @@
         <v>-154.2809</v>
       </c>
       <c r="P18" t="n">
-        <v>-39.54209999999999</v>
+        <v>-39.5421</v>
       </c>
       <c r="Q18" t="n">
         <v>-377.7361</v>
@@ -1858,13 +1858,13 @@
         <v>338.1926</v>
       </c>
       <c r="S18" t="n">
-        <v>-32.1152</v>
+        <v>-3.692299999999998</v>
       </c>
       <c r="T18" t="n">
-        <v>3.093699999999998</v>
+        <v>12.2273</v>
       </c>
       <c r="U18" t="n">
-        <v>-35.2069</v>
+        <v>-15.9192</v>
       </c>
       <c r="V18" t="n">
         <v>39.59</v>
